--- a/Partial-Entries-Converted-to-Apps/06-29-26-ford-partials-converted-to-apps-this-week.xlsx
+++ b/Partial-Entries-Converted-to-Apps/06-29-26-ford-partials-converted-to-apps-this-week.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.9" customWidth="1" min="1" max="1"/>
     <col width="15.4" customWidth="1" min="2" max="2"/>
-    <col width="14.3" customWidth="1" min="3" max="3"/>
-    <col width="36.3" customWidth="1" min="4" max="4"/>
+    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="37.40000000000001" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -455,216 +455,189 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003QP000019KdAx</t>
+          <t>003QP00001c3cyQ</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Penelope</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Jesuis</t>
+          <t>Dubula</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>karin@karinjesuis.com</t>
+          <t>dubulap9@gmail.com</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bEfjq</t>
+          <t>003QP00001ACmLK</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Ramogale</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>luisosorno01@gmail.com</t>
+          <t>ramogalejm@gmail.com</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>06-16-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bLURu</t>
+          <t>003QP00001cHsvK</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Phyo Min</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Leblanc</t>
+          <t>Maung Maung</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>esther@institutofoz.org</t>
+          <t>phyominmaungmaungmwd@gmail.com</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bOZlE</t>
+          <t>003QP000002AY2T</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Galan</t>
+          <t>Witbooi</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>andresgalanc@gmail.com</t>
+          <t>steven.witbooi@gmail.com</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bYMQC</t>
+          <t>003QP000019Kcsa</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>laurag@sanaencasa.org</t>
+          <t>stanley.jones@reach.org.vn</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-25-2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0033h000018iG2W</t>
+          <t>0033h00001I3xvr</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Diogo</t>
+          <t>Olufunke</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Silva</t>
+          <t>Oyedun</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>diogobezerra@mais1code.com.br</t>
+          <t>olufunkeoyedun@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>06-19-2026</t>
+          <t>06-29-2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bsDTx</t>
+          <t>003QP00001cvmnv</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Zamile</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Figueroa</t>
+          <t>Hlongwana</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>laura@impactclick.org</t>
+          <t>zamile@yeboinstitute.org</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>06-20-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>003QP00000g3H2X</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Wesam</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Qatawna</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>wesamqataweneh@gmail.com</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>06-21-2026</t>
+          <t>06-29-2026</t>
         </is>
       </c>
     </row>
